--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-clinical-document.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-clinical-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="202">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T11:16:18+00:00</t>
+    <t>2025-08-22T11:39:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,6 +260,10 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PerformerRequire:performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal {documentationOf.serviceEvent.performer.count() &gt;= 1}
+</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1194,25 +1198,25 @@
         <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>80</v>
@@ -1230,11 +1234,11 @@
         <v>74</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1261,11 +1265,11 @@
         <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>74</v>
@@ -1283,7 +1287,7 @@
         <v>74</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
@@ -1303,10 +1307,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1329,7 +1333,7 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -1340,7 +1344,7 @@
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S4" t="s" s="2">
         <v>74</v>
@@ -1358,11 +1362,11 @@
         <v>74</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y4" s="2"/>
       <c r="Z4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA4" t="s" s="2">
         <v>74</v>
@@ -1380,7 +1384,7 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
@@ -1400,10 +1404,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1426,7 +1430,7 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -1437,7 +1441,7 @@
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S5" t="s" s="2">
         <v>74</v>
@@ -1455,11 +1459,11 @@
         <v>74</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y5" s="2"/>
       <c r="Z5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>74</v>
@@ -1477,7 +1481,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -1497,10 +1501,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1523,13 +1527,13 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1580,7 +1584,7 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -1600,10 +1604,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1626,13 +1630,13 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1683,7 +1687,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1703,17 +1707,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1731,11 +1735,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1762,11 +1766,11 @@
         <v>74</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y8" s="2"/>
       <c r="Z8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>74</v>
@@ -1784,7 +1788,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1804,17 +1808,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>80</v>
@@ -1832,11 +1836,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1887,7 +1891,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1907,17 +1911,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>80</v>
@@ -1935,11 +1939,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1990,7 +1994,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2010,17 +2014,17 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>75</v>
@@ -2038,11 +2042,11 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2051,7 +2055,7 @@
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="S11" t="s" s="2">
         <v>74</v>
@@ -2093,7 +2097,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2113,17 +2117,17 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>75</v>
@@ -2141,11 +2145,11 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2154,7 +2158,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2196,7 +2200,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2216,10 +2220,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2227,7 +2231,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>81</v>
@@ -2242,13 +2246,13 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2299,7 +2303,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2319,10 +2323,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2345,10 +2349,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2400,7 +2404,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2420,10 +2424,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2446,10 +2450,10 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -2477,11 +2481,11 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2499,7 +2503,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2519,10 +2523,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2545,10 +2549,10 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -2600,7 +2604,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2620,10 +2624,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2646,11 +2650,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2677,11 +2681,11 @@
         <v>74</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>74</v>
@@ -2699,7 +2703,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2719,10 +2723,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2745,10 +2749,10 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -2800,7 +2804,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -2820,10 +2824,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2846,10 +2850,10 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -2901,7 +2905,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -2921,10 +2925,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2947,10 +2951,10 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -2978,11 +2982,11 @@
         <v>74</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -3000,7 +3004,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3020,10 +3024,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3046,10 +3050,10 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -3101,7 +3105,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3121,10 +3125,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3147,10 +3151,10 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -3202,7 +3206,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3222,10 +3226,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3248,7 +3252,7 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -3301,7 +3305,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3321,10 +3325,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3347,10 +3351,10 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -3402,7 +3406,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3422,10 +3426,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3448,10 +3452,10 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -3503,7 +3507,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -3523,10 +3527,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3549,10 +3553,10 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -3604,7 +3608,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3624,10 +3628,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3650,10 +3654,10 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -3705,7 +3709,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3725,10 +3729,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3751,10 +3755,10 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -3806,7 +3810,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -3826,10 +3830,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3852,10 +3856,10 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -3907,7 +3911,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -3927,10 +3931,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3953,10 +3957,10 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -4008,7 +4012,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4028,10 +4032,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4054,10 +4058,10 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -4109,7 +4113,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4129,10 +4133,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4155,10 +4159,10 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -4210,7 +4214,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4230,10 +4234,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4256,10 +4260,10 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -4311,7 +4315,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4331,10 +4335,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4357,10 +4361,10 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -4412,7 +4416,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4432,10 +4436,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4458,10 +4462,10 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -4513,7 +4517,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4533,10 +4537,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4559,10 +4563,10 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
@@ -4614,7 +4618,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4634,10 +4638,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4660,10 +4664,10 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -4715,7 +4719,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4735,10 +4739,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4761,7 +4765,7 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -4814,7 +4818,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-clinical-document.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-clinical-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T11:39:32+00:00</t>
+    <t>2025-08-22T13:00:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-clinical-document.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-clinical-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="201">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T13:00:58+00:00</t>
+    <t>2025-08-22T15:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,10 +260,6 @@
   </si>
   <si>
     <t>*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PerformerRequire:performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal {documentationOf.serviceEvent.performer.count() &gt;= 1}
-</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1198,25 +1194,25 @@
         <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>80</v>
@@ -1234,11 +1230,11 @@
         <v>74</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1265,29 +1261,29 @@
         <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF3" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF3" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
@@ -1307,10 +1303,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1333,7 +1329,7 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -1344,29 +1340,29 @@
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="S4" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T4" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U4" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V4" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W4" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X4" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="S4" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T4" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U4" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V4" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W4" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X4" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="Y4" s="2"/>
       <c r="Z4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA4" t="s" s="2">
         <v>74</v>
@@ -1384,7 +1380,7 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
@@ -1404,10 +1400,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1430,7 +1426,7 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -1441,7 +1437,7 @@
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S5" t="s" s="2">
         <v>74</v>
@@ -1459,11 +1455,11 @@
         <v>74</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y5" s="2"/>
       <c r="Z5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>74</v>
@@ -1481,7 +1477,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -1501,10 +1497,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1527,13 +1523,13 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>101</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1584,7 +1580,7 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -1604,10 +1600,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1630,13 +1626,13 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1687,7 +1683,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1707,17 +1703,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1735,11 +1731,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1766,29 +1762,29 @@
         <v>74</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y8" s="2"/>
       <c r="Z8" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF8" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1808,17 +1804,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>80</v>
@@ -1836,11 +1832,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1891,7 +1887,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1911,17 +1907,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>80</v>
@@ -1939,11 +1935,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1994,7 +1990,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2014,39 +2010,39 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E11" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K11" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="F11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K11" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2055,49 +2051,49 @@
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF11" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="S11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2117,17 +2113,17 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>75</v>
@@ -2145,11 +2141,11 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2158,49 +2154,49 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2220,10 +2216,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2231,7 +2227,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>81</v>
@@ -2246,13 +2242,13 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2303,7 +2299,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2323,10 +2319,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2349,10 +2345,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2404,7 +2400,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2424,10 +2420,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2450,10 +2446,10 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -2481,11 +2477,11 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2503,7 +2499,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2523,10 +2519,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2549,10 +2545,10 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -2604,7 +2600,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2624,10 +2620,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2650,11 +2646,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2681,11 +2677,11 @@
         <v>74</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>74</v>
@@ -2703,7 +2699,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2723,10 +2719,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2749,10 +2745,10 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -2804,7 +2800,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -2824,10 +2820,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2850,10 +2846,10 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -2905,7 +2901,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -2925,10 +2921,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2951,10 +2947,10 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -2982,11 +2978,11 @@
         <v>74</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -3004,7 +3000,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3024,10 +3020,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3050,10 +3046,10 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -3105,7 +3101,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3125,10 +3121,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3151,10 +3147,10 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -3206,7 +3202,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3226,10 +3222,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3252,7 +3248,7 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -3305,7 +3301,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3325,10 +3321,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3351,10 +3347,10 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -3406,7 +3402,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3426,10 +3422,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3452,10 +3448,10 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -3507,7 +3503,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -3527,10 +3523,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3553,10 +3549,10 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -3608,7 +3604,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3628,10 +3624,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3654,10 +3650,10 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -3709,7 +3705,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3729,10 +3725,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3755,10 +3751,10 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -3810,7 +3806,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -3830,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3856,10 +3852,10 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -3911,7 +3907,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -3931,10 +3927,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3957,10 +3953,10 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -4012,7 +4008,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4032,10 +4028,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4058,10 +4054,10 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -4113,7 +4109,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4133,10 +4129,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4159,10 +4155,10 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -4214,7 +4210,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4234,10 +4230,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4260,10 +4256,10 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -4315,7 +4311,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4335,10 +4331,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4361,10 +4357,10 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -4416,7 +4412,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4436,10 +4432,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4462,10 +4458,10 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -4517,7 +4513,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4537,10 +4533,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4563,10 +4559,10 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
@@ -4618,7 +4614,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4638,10 +4634,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4664,10 +4660,10 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -4719,7 +4715,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4739,10 +4735,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4765,7 +4761,7 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -4818,7 +4814,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-clinical-document.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-clinical-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="202">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T15:38:31+00:00</t>
+    <t>2025-08-22T16:16:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,6 +260,10 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PerformerRequire:performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal {performer.exists()}
+</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1194,25 +1198,25 @@
         <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>80</v>
@@ -1230,11 +1234,11 @@
         <v>74</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1261,11 +1265,11 @@
         <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>74</v>
@@ -1283,7 +1287,7 @@
         <v>74</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
@@ -1303,10 +1307,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1329,7 +1333,7 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -1340,7 +1344,7 @@
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S4" t="s" s="2">
         <v>74</v>
@@ -1358,11 +1362,11 @@
         <v>74</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y4" s="2"/>
       <c r="Z4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA4" t="s" s="2">
         <v>74</v>
@@ -1380,7 +1384,7 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
@@ -1400,10 +1404,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1426,7 +1430,7 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -1437,7 +1441,7 @@
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S5" t="s" s="2">
         <v>74</v>
@@ -1455,11 +1459,11 @@
         <v>74</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y5" s="2"/>
       <c r="Z5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>74</v>
@@ -1477,7 +1481,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -1497,10 +1501,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1523,13 +1527,13 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1580,7 +1584,7 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -1600,10 +1604,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1626,13 +1630,13 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1683,7 +1687,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1703,17 +1707,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1731,11 +1735,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1762,11 +1766,11 @@
         <v>74</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y8" s="2"/>
       <c r="Z8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>74</v>
@@ -1784,7 +1788,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1804,17 +1808,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>80</v>
@@ -1832,11 +1836,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1887,7 +1891,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1907,17 +1911,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>80</v>
@@ -1935,11 +1939,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1990,7 +1994,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2010,17 +2014,17 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>75</v>
@@ -2038,11 +2042,11 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2051,7 +2055,7 @@
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="S11" t="s" s="2">
         <v>74</v>
@@ -2093,7 +2097,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2113,17 +2117,17 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>75</v>
@@ -2141,11 +2145,11 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2154,7 +2158,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2196,7 +2200,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2216,10 +2220,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2227,7 +2231,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>81</v>
@@ -2242,13 +2246,13 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2299,7 +2303,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2319,10 +2323,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2345,10 +2349,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2400,7 +2404,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2420,10 +2424,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2446,10 +2450,10 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -2477,11 +2481,11 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2499,7 +2503,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2519,10 +2523,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2545,10 +2549,10 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -2600,7 +2604,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2620,10 +2624,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2646,11 +2650,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2677,11 +2681,11 @@
         <v>74</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>74</v>
@@ -2699,7 +2703,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2719,10 +2723,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2745,10 +2749,10 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -2800,7 +2804,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -2820,10 +2824,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2846,10 +2850,10 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -2901,7 +2905,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -2921,10 +2925,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2947,10 +2951,10 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -2978,11 +2982,11 @@
         <v>74</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -3000,7 +3004,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3020,10 +3024,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3046,10 +3050,10 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -3101,7 +3105,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3121,10 +3125,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3147,10 +3151,10 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -3202,7 +3206,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3222,10 +3226,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3248,7 +3252,7 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -3301,7 +3305,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3321,10 +3325,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3347,10 +3351,10 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -3402,7 +3406,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3422,10 +3426,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3448,10 +3452,10 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -3503,7 +3507,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -3523,10 +3527,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3549,10 +3553,10 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -3604,7 +3608,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3624,10 +3628,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3650,10 +3654,10 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -3705,7 +3709,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3725,10 +3729,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3751,10 +3755,10 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -3806,7 +3810,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -3826,10 +3830,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3852,10 +3856,10 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -3907,7 +3911,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -3927,10 +3931,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3953,10 +3957,10 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -4008,7 +4012,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4028,10 +4032,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4054,10 +4058,10 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -4109,7 +4113,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4129,10 +4133,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4155,10 +4159,10 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -4210,7 +4214,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4230,10 +4234,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4256,10 +4260,10 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -4311,7 +4315,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4331,10 +4335,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4357,10 +4361,10 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -4412,7 +4416,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4432,10 +4436,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4458,10 +4462,10 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -4513,7 +4517,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4533,10 +4537,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4559,10 +4563,10 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
@@ -4614,7 +4618,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4634,10 +4638,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4660,10 +4664,10 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -4715,7 +4719,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4735,10 +4739,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4761,7 +4765,7 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -4814,7 +4818,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-clinical-document.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-clinical-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T16:16:41+00:00</t>
+    <t>2025-08-25T07:57:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -262,7 +262,7 @@
     <t>*</t>
   </si>
   <si>
-    <t xml:space="preserve">PerformerRequire:performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal {performer.exists()}
+    <t xml:space="preserve">PerformerRequire:performer est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal {documentationOf.serviceEvent.performer.count() &gt;= 1}
 </t>
   </si>
   <si>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-clinical-document.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-clinical-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T07:57:03+00:00</t>
+    <t>2025-08-25T14:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
